--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_332_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_332_R34.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6466</v>
+        <v>4.4328</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5565</v>
+        <v>2.8913</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0901</v>
+        <v>1.5415</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5917</v>
+        <v>4.0535</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0999</v>
+        <v>0.4464</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4918</v>
+        <v>3.607</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1062</v>
+        <v>4.0321</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1196</v>
+        <v>0.7331</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0134</v>
+        <v>3.299</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6978</v>
+        <v>0.0214</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2195</v>
+        <v>-0.2866</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4783</v>
+        <v>0.308</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7021</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3961</v>
+        <v>0.3385</v>
       </c>
       <c r="U2" t="n">
-        <v>1.306</v>
+        <v>0.5048</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2862</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.97</v>
+        <v>4.2467</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2269</v>
+        <v>3.5263</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7431</v>
+        <v>0.7204</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0535</v>
+        <v>-0.5917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4464</v>
+        <v>-0.0999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.607</v>
+        <v>-0.4918</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0321</v>
+        <v>1.1062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7331</v>
+        <v>1.1196</v>
       </c>
       <c r="L3" t="n">
-        <v>3.299</v>
+        <v>-0.0134</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0214</v>
+        <v>-1.6978</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2866</v>
+        <v>-1.2195</v>
       </c>
       <c r="O3" t="n">
-        <v>0.308</v>
+        <v>-0.4783</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3804</v>
+        <v>1.3023</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.326</v>
+        <v>0.3659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7064</v>
+        <v>0.9364</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2304</v>
+        <v>3.7262</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7553</v>
+        <v>3.1838</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4751</v>
+        <v>0.5423</v>
       </c>
       <c r="G4" t="n">
         <v>1.7113</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3593</v>
+        <v>0.8551</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1221</v>
+        <v>0.5507</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2372</v>
+        <v>0.3044</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6136</v>
+        <v>1.4226</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0003</v>
+        <v>1.4404</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3867</v>
+        <v>-0.0178</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3712</v>
+        <v>0.1163</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9363</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4349</v>
+        <v>0.9002</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2515</v>
+        <v>1.7822</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1043</v>
+        <v>0.4572</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>1.325</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6227</v>
+        <v>-1.6659</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0406</v>
+        <v>-1.241</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5821</v>
+        <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.057</v>
+        <v>0.1465</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9085</v>
+        <v>-0.1098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1485</v>
+        <v>0.2563</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3645</v>
+        <v>0.5674</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8192</v>
+        <v>1.1429</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4547</v>
+        <v>-0.5755</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1163</v>
+        <v>-4.7017</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-1.0143</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9002</v>
+        <v>-3.6874</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7822</v>
+        <v>-2.3181</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4572</v>
+        <v>-0.5812</v>
       </c>
       <c r="L6" t="n">
-        <v>1.325</v>
+        <v>-1.7369</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6659</v>
+        <v>-2.3837</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.241</v>
+        <v>-0.4331</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4248</v>
+        <v>-1.9505</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9116</v>
+        <v>0.519</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.731</v>
+        <v>0.1026</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1805</v>
+        <v>0.4165</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3263</v>
+        <v>-0.003</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5877</v>
+        <v>1.2493</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2614</v>
+        <v>-1.2523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1096</v>
+        <v>-1.3712</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8929</v>
+        <v>-0.9363</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7833</v>
+        <v>-0.4349</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9779</v>
+        <v>0.2515</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6539</v>
+        <v>0.1043</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8683</v>
+        <v>-1.6227</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2391</v>
+        <v>-1.0406</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1074</v>
+        <v>-0.5821</v>
       </c>
       <c r="P7" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5209</v>
+        <v>0.4404</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7695</v>
+        <v>0.1575</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2486</v>
+        <v>0.2829</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
         <v>-1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0703</v>
+        <v>-0.5262</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6397</v>
+        <v>0.6008</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7099</v>
+        <v>-1.127</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.7017</v>
+        <v>0.1096</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0143</v>
+        <v>1.8929</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.6874</v>
+        <v>-1.7833</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3181</v>
+        <v>0.9779</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5812</v>
+        <v>1.6539</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7369</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3837</v>
+        <v>-0.8683</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4331</v>
+        <v>0.2391</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9505</v>
+        <v>-1.1074</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1186</v>
+        <v>0.6684</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4007</v>
+        <v>0.7826</v>
       </c>
       <c r="U8" t="n">
-        <v>0.282</v>
+        <v>-0.1142</v>
       </c>
       <c r="V8" t="n">
-        <v>3.3584</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6111</v>
+        <v>-0.6373</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6555</v>
+        <v>-0.5808</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0444</v>
+        <v>-0.0564</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9072</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V9" t="n">
         <v>0.6778999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.037</v>
+        <v>-2.582</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7612</v>
+        <v>-1.8145</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2758</v>
+        <v>-0.7675</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0605</v>
+        <v>-2.8904</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5584</v>
+        <v>-1.5787</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6189</v>
+        <v>-1.3117</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0729</v>
+        <v>-2.1685</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3466</v>
+        <v>-1.6497</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7263</v>
+        <v>-0.5188</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0123</v>
+        <v>-0.7219</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9049</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1074</v>
+        <v>-0.7929</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3295</v>
+        <v>0.5946</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8883</v>
+        <v>0.3541</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5588</v>
+        <v>0.2405</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.214</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5741</v>
+        <v>-2.6682</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9074</v>
+        <v>-1.2579</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6667</v>
+        <v>-1.4103</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8904</v>
+        <v>0.0605</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5787</v>
+        <v>-0.5584</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3117</v>
+        <v>0.6189</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1685</v>
+        <v>2.0729</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6497</v>
+        <v>0.3466</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5188</v>
+        <v>1.7263</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7219</v>
+        <v>-2.0123</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.9049</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7929</v>
+        <v>-1.1074</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3976</v>
+        <v>0.0393</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3413</v>
+        <v>0.4244</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8589</v>
+        <v>7.979000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.261500000000002</v>
+        <v>10.3816</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.402499999999999</v>
+        <v>-2.402599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-4.411</v>
@@ -1360,13 +1360,13 @@
         <v>-0.4629999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.948099999999999</v>
+        <v>-3.9481</v>
       </c>
       <c r="J12" t="n">
         <v>8.4198</v>
       </c>
       <c r="K12" t="n">
-        <v>4.439099999999999</v>
+        <v>4.439099999999998</v>
       </c>
       <c r="L12" t="n">
         <v>3.9807</v>
@@ -1381,7 +1381,7 @@
         <v>-7.9287</v>
       </c>
       <c r="P12" t="n">
-        <v>4.639000000000001</v>
+        <v>4.639</v>
       </c>
       <c r="Q12" t="n">
         <v>-8.118600000000001</v>
@@ -1390,19 +1390,19 @@
         <v>12.7575</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3445</v>
+        <v>5.464799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8872999999999999</v>
+        <v>2.0076</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4573</v>
+        <v>3.4574</v>
       </c>
       <c r="V12" t="n">
         <v>2.2862</v>
       </c>
       <c r="W12" t="n">
-        <v>8.0726</v>
+        <v>8.072600000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-5.7864</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3224</v>
+        <v>4.2172</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6765</v>
+        <v>3.7944</v>
       </c>
       <c r="F13" t="n">
-        <v>0.646</v>
+        <v>0.4228</v>
       </c>
       <c r="G13" t="n">
         <v>3.2031</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4235</v>
+        <v>0.3183</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1954</v>
+        <v>3.1668</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9194</v>
+        <v>2.5656</v>
       </c>
       <c r="F14" t="n">
-        <v>0.276</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3.2532</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.344</v>
+        <v>-0.3725</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0474</v>
+        <v>-0.3064</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3914</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5219</v>
+        <v>2.695</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2832</v>
+        <v>1.873</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2386</v>
+        <v>0.822</v>
       </c>
       <c r="G15" t="n">
         <v>3.0644</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6843</v>
+        <v>-0.5111</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8707</v>
+        <v>-0.2873</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.431</v>
+        <v>-0.1615</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8922</v>
+        <v>1.1281</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3232</v>
+        <v>-1.2896</v>
       </c>
       <c r="G16" t="n">
         <v>1.0001</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8228</v>
+        <v>-0.5533</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5878</v>
+        <v>-0.7736</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5206</v>
+        <v>-0.8744</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0672</v>
+        <v>0.1008</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8061</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4503</v>
+        <v>0.2645</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3383</v>
+        <v>-0.0156</v>
       </c>
       <c r="U17" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3251</v>
+        <v>-0.8475</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2286</v>
+        <v>-1.8748</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9036</v>
+        <v>1.0272</v>
       </c>
       <c r="G18" t="n">
         <v>0.09760000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2113</v>
+        <v>0.2662</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1621</v>
+        <v>0.2858</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2836</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4542</v>
+        <v>-1.3027</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7021</v>
+        <v>1.82</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1563</v>
+        <v>-3.1227</v>
       </c>
       <c r="G19" t="n">
         <v>1.6035</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1453</v>
+        <v>-0.9937</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.963</v>
+        <v>-0.845</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1823</v>
+        <v>-0.1487</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1444</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7763</v>
+        <v>-2.6964</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8485</v>
+        <v>-1.5562</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-1.1403</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7485</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9722</v>
+        <v>0.0521</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8259</v>
+        <v>0.1182</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1463</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9018</v>
+        <v>-3.0483</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9638</v>
+        <v>-1.4356</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.938</v>
+        <v>-1.6127</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4086</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.7145</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1098</v>
+        <v>-0.5816</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4582</v>
+        <v>-0.1329</v>
       </c>
       <c r="V21" t="n">
         <v>0.9304</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0912</v>
+        <v>-3.0576</v>
       </c>
       <c r="E22" t="n">
         <v>-1.2024</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8888</v>
+        <v>-1.8552</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7556</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1129</v>
+        <v>0.1465</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2592</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3311</v>
+        <v>-3.4775</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3792</v>
+        <v>-2.9074</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9519</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.092</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5279</v>
+        <v>-0.6743</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8136</v>
+        <v>-0.3418</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7143</v>
+        <v>-0.3325</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.858800000000001</v>
+        <v>-5.286099999999999</v>
       </c>
       <c r="E24" t="n">
         <v>1.3303</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.1891</v>
+        <v>-6.6165</v>
       </c>
       <c r="G24" t="n">
         <v>4.411100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>8.118599999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.3447</v>
+        <v>-2.7718</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.4574</v>
+        <v>-3.4573</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8874</v>
+        <v>0.6854</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2862</v>
